--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-personne-structure-auteur.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="122">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,6 +263,26 @@
     <t>Personne</t>
   </si>
   <si>
+    <t>fr-lm-personne-structure-auteur.personne.roleFonctionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Rôle fonctionnel de l’auteur. A utiliser uniquement si l'auteur est un professionnel.</t>
+  </si>
+  <si>
+    <t>fr-lm-personne-structure-auteur.personne.horodatageParticipation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time
+</t>
+  </si>
+  <si>
+    <t>Horodatage de la participation de l’auteur.</t>
+  </si>
+  <si>
     <t>fr-lm-personne-structure-auteur.personne.identifiantPersonne</t>
   </si>
   <si>
@@ -274,10 +294,6 @@
   </si>
   <si>
     <t>fr-lm-personne-structure-auteur.personne.professionRole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -679,7 +695,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.64453125" customWidth="true" bestFit="true"/>
@@ -1042,10 +1058,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>73</v>
@@ -1117,10 +1133,10 @@
         <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>73</v>
@@ -1142,7 +1158,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>79</v>
@@ -1217,7 +1233,7 @@
         <v>85</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>79</v>
@@ -1242,7 +1258,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>75</v>
@@ -1317,7 +1333,7 @@
         <v>88</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>75</v>
@@ -1345,7 +1361,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1357,13 +1373,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L7" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1420,7 +1436,7 @@
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1431,10 +1447,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1442,10 +1458,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1457,7 +1473,7 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>95</v>
@@ -1514,13 +1530,13 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1542,7 +1558,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>75</v>
@@ -1557,13 +1573,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1617,7 +1633,7 @@
         <v>96</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>75</v>
@@ -1631,10 +1647,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1642,10 +1658,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -1657,7 +1673,7 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>100</v>
@@ -1714,13 +1730,13 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>73</v>
@@ -1742,10 +1758,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1757,7 +1773,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>102</v>
@@ -1817,10 +1833,10 @@
         <v>101</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
@@ -1845,7 +1861,7 @@
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -1857,13 +1873,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1920,7 +1936,7 @@
         <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
@@ -1931,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1957,13 +1973,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2014,7 +2030,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2031,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2060,10 +2076,10 @@
         <v>83</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2114,7 +2130,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2131,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2157,13 +2173,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2214,7 +2230,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2231,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2245,7 +2261,7 @@
         <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
@@ -2260,10 +2276,10 @@
         <v>89</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2314,13 +2330,13 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>73</v>
@@ -2331,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2345,7 +2361,7 @@
         <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>73</v>
@@ -2357,13 +2373,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2414,13 +2430,13 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>73</v>
@@ -2431,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2445,7 +2461,7 @@
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>73</v>
@@ -2457,13 +2473,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2514,18 +2530,218 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>73</v>
       </c>
     </row>
